--- a/ig/DM-OCTOBRE-2026/CodeSystem-concept-properties.xlsx
+++ b/ig/DM-OCTOBRE-2026/CodeSystem-concept-properties.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="165">
   <si>
     <t>Property</t>
   </si>
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260629120000</t>
+    <t>20261102120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T12:00:00.000+00:00</t>
+    <t>2026-11-02T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -115,7 +115,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>37</t>
+    <t>40</t>
   </si>
   <si>
     <t>Code</t>
@@ -482,6 +482,33 @@
   </si>
   <si>
     <t>Permet de définir les codes à inclure dans le JDV_J83-AutoriteEnregistrement-RASS</t>
+  </si>
+  <si>
+    <t>activiteReconnaisanceEcars</t>
+  </si>
+  <si>
+    <t>Activité Reconnaisance E-CARS</t>
+  </si>
+  <si>
+    <t>Propriété permettant de renseigner les activités soumises à reconnaissances (ASR)</t>
+  </si>
+  <si>
+    <t>modaliteEcars</t>
+  </si>
+  <si>
+    <t>Modalité E-CARS</t>
+  </si>
+  <si>
+    <t>Propriété permettant de renseigner les modalités des activités autorisées /exercées provenant d'E-CARS</t>
+  </si>
+  <si>
+    <t>formeEcars</t>
+  </si>
+  <si>
+    <t>Forme E-CARS</t>
+  </si>
+  <si>
+    <t>Propriété permettant de renseigner les formes des activités autorisées /exercées provenant d'E-CARS</t>
   </si>
 </sst>
 </file>
@@ -821,7 +848,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D38"/>
+  <dimension ref="A1:D41"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1356,6 +1383,48 @@
         <v>155</v>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="B39" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="C39" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="D39" t="s" s="2">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="B40" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="C40" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="D40" t="s" s="2">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="B41" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="C41" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="D41" t="s" s="2">
+        <v>164</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/ig/DM-OCTOBRE-2026/CodeSystem-concept-properties.xlsx
+++ b/ig/DM-OCTOBRE-2026/CodeSystem-concept-properties.xlsx
@@ -484,31 +484,31 @@
     <t>Permet de définir les codes à inclure dans le JDV_J83-AutoriteEnregistrement-RASS</t>
   </si>
   <si>
-    <t>activiteReconnaisanceEcars</t>
-  </si>
-  <si>
-    <t>Activité Reconnaisance E-CARS</t>
+    <t>activiteReconnaisanceContractuelle</t>
+  </si>
+  <si>
+    <t>Activité Reconnaisance Contractuelle</t>
   </si>
   <si>
     <t>Propriété permettant de renseigner les activités soumises à reconnaissances (ASR)</t>
   </si>
   <si>
-    <t>modaliteEcars</t>
-  </si>
-  <si>
-    <t>Modalité E-CARS</t>
-  </si>
-  <si>
-    <t>Propriété permettant de renseigner les modalités des activités autorisées /exercées provenant d'E-CARS</t>
-  </si>
-  <si>
-    <t>formeEcars</t>
-  </si>
-  <si>
-    <t>Forme E-CARS</t>
-  </si>
-  <si>
-    <t>Propriété permettant de renseigner les formes des activités autorisées /exercées provenant d'E-CARS</t>
+    <t>modaliteReconnaissanceContractuelle</t>
+  </si>
+  <si>
+    <t>Modalité Reconnaisance Contractuelle</t>
+  </si>
+  <si>
+    <t>Propriété permettant de renseigner les modalités des activités autorisées /exercées provenant provenant d'E-CARS</t>
+  </si>
+  <si>
+    <t>formeReconnaissanceContractuelle</t>
+  </si>
+  <si>
+    <t>Forme Reconnaisance Contractuelle</t>
+  </si>
+  <si>
+    <t>Propriété permettant de renseigner les formes des activités autorisées /exercées provenant provenant d'E-CARS</t>
   </si>
 </sst>
 </file>
